--- a/AAII_Financials/Yearly/ARDT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARDT_YR_FIN.xlsx
@@ -2174,7 +2174,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>76900</v>
+        <v>78700</v>
       </c>
       <c r="E58" s="3">
         <v>55600</v>
@@ -2207,7 +2207,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>121600</v>
+        <v>119800</v>
       </c>
       <c r="E59" s="3">
         <v>124700</v>
@@ -2273,7 +2273,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2241000</v>
+        <v>2247000</v>
       </c>
       <c r="E61" s="3">
         <v>2226600</v>
@@ -2306,7 +2306,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>317700</v>
+        <v>311700</v>
       </c>
       <c r="E62" s="3">
         <v>261700</v>
